--- a/research/traditional_assets/database/data/tunisia/tunisia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_bank_money_center.xlsx
@@ -600,28 +600,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>29.7</v>
+        <v>37.2</v>
       </c>
       <c r="L2">
-        <v>0.2129032258064516</v>
+        <v>0.2717311906501096</v>
       </c>
       <c r="M2">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="N2">
-        <v>1.589825119236884e-05</v>
+        <v>3.743916136278547e-06</v>
       </c>
       <c r="O2">
-        <v>0.000101010101010101</v>
+        <v>2.688172043010753e-05</v>
       </c>
       <c r="P2">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="Q2">
-        <v>1.589825119236884e-05</v>
+        <v>3.743916136278547e-06</v>
       </c>
       <c r="R2">
-        <v>0.000101010101010101</v>
+        <v>2.688172043010753e-05</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,55 +630,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>47.6</v>
+        <v>46.3</v>
       </c>
       <c r="V2">
-        <v>0.2522522522522523</v>
+        <v>0.1733433171096967</v>
       </c>
       <c r="W2">
-        <v>0.145945945945946</v>
+        <v>0.1482662415304903</v>
       </c>
       <c r="X2">
-        <v>0.1170411091587753</v>
+        <v>0.143962184879353</v>
       </c>
       <c r="Y2">
-        <v>0.02890483678717065</v>
+        <v>0.004304056651137284</v>
       </c>
       <c r="Z2">
-        <v>0.5443031553975756</v>
+        <v>0.4321447511300791</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1009000242611968</v>
+        <v>0.140236647295106</v>
       </c>
       <c r="AC2">
-        <v>-0.1009000242611968</v>
+        <v>-0.140236647295106</v>
       </c>
       <c r="AD2">
-        <v>113.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>113.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>65.90000000000001</v>
+        <v>34.8</v>
       </c>
       <c r="AH2">
-        <v>0.3755790866975513</v>
+        <v>0.232912119471568</v>
       </c>
       <c r="AI2">
-        <v>0.3114709110867179</v>
+        <v>0.2416567342073897</v>
       </c>
       <c r="AJ2">
-        <v>0.2588373919874313</v>
+        <v>0.1152699569393839</v>
       </c>
       <c r="AK2">
-        <v>0.2080176767676768</v>
+        <v>0.1202903560318009</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -716,28 +716,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>29.7</v>
+        <v>37.2</v>
       </c>
       <c r="L3">
-        <v>0.2129032258064516</v>
+        <v>0.2717311906501096</v>
       </c>
       <c r="M3">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="N3">
-        <v>1.589825119236884e-05</v>
+        <v>3.743916136278547e-06</v>
       </c>
       <c r="O3">
-        <v>0.000101010101010101</v>
+        <v>2.688172043010753e-05</v>
       </c>
       <c r="P3">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="Q3">
-        <v>1.589825119236884e-05</v>
+        <v>3.743916136278547e-06</v>
       </c>
       <c r="R3">
-        <v>0.000101010101010101</v>
+        <v>2.688172043010753e-05</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -746,55 +746,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>47.6</v>
+        <v>46.3</v>
       </c>
       <c r="V3">
-        <v>0.2522522522522523</v>
+        <v>0.1733433171096967</v>
       </c>
       <c r="W3">
-        <v>0.145945945945946</v>
+        <v>0.1482662415304903</v>
       </c>
       <c r="X3">
-        <v>0.1170411091587753</v>
+        <v>0.143962184879353</v>
       </c>
       <c r="Y3">
-        <v>0.02890483678717065</v>
+        <v>0.004304056651137284</v>
       </c>
       <c r="Z3">
-        <v>0.5443031553975756</v>
+        <v>0.4321447511300791</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1009000242611968</v>
+        <v>0.140236647295106</v>
       </c>
       <c r="AC3">
-        <v>-0.1009000242611968</v>
+        <v>-0.140236647295106</v>
       </c>
       <c r="AD3">
-        <v>113.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>113.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>65.90000000000001</v>
+        <v>34.8</v>
       </c>
       <c r="AH3">
-        <v>0.3755790866975513</v>
+        <v>0.232912119471568</v>
       </c>
       <c r="AI3">
-        <v>0.3114709110867179</v>
+        <v>0.2416567342073897</v>
       </c>
       <c r="AJ3">
-        <v>0.2588373919874313</v>
+        <v>0.1152699569393839</v>
       </c>
       <c r="AK3">
-        <v>0.2080176767676768</v>
+        <v>0.1202903560318009</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/tunisia/tunisia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_bank_money_center.xlsx
@@ -587,6 +587,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.105</v>
+      </c>
+      <c r="E2">
+        <v>0.09</v>
+      </c>
       <c r="G2">
         <v>0</v>
       </c>
@@ -600,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>37.2</v>
+        <v>42.7</v>
       </c>
       <c r="L2">
-        <v>0.2717311906501096</v>
+        <v>0.2896879240162822</v>
       </c>
       <c r="M2">
-        <v>0.001</v>
+        <v>7.8</v>
       </c>
       <c r="N2">
-        <v>3.743916136278547e-06</v>
+        <v>0.02672147995889003</v>
       </c>
       <c r="O2">
-        <v>2.688172043010753e-05</v>
+        <v>0.1826697892271663</v>
       </c>
       <c r="P2">
-        <v>0.001</v>
+        <v>7.8</v>
       </c>
       <c r="Q2">
-        <v>3.743916136278547e-06</v>
+        <v>0.02672147995889003</v>
       </c>
       <c r="R2">
-        <v>2.688172043010753e-05</v>
+        <v>0.1826697892271663</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>46.3</v>
+        <v>59.3</v>
       </c>
       <c r="V2">
-        <v>0.1733433171096967</v>
+        <v>0.2031517643028435</v>
       </c>
       <c r="W2">
-        <v>0.1482662415304903</v>
+        <v>0.157390342793955</v>
       </c>
       <c r="X2">
-        <v>0.143962184879353</v>
+        <v>0.1233396199045744</v>
       </c>
       <c r="Y2">
-        <v>0.004304056651137284</v>
+        <v>0.03405072288938064</v>
       </c>
       <c r="Z2">
-        <v>0.4321447511300791</v>
+        <v>0.4484427718265981</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.140236647295106</v>
+        <v>0.1230077050576663</v>
       </c>
       <c r="AC2">
-        <v>-0.140236647295106</v>
+        <v>-0.1230077050576663</v>
       </c>
       <c r="AD2">
-        <v>81.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>81.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="AG2">
-        <v>34.8</v>
+        <v>12.40000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.232912119471568</v>
+        <v>0.1971947194719472</v>
       </c>
       <c r="AI2">
-        <v>0.2416567342073897</v>
+        <v>0.1995546896743668</v>
       </c>
       <c r="AJ2">
-        <v>0.1152699569393839</v>
+        <v>0.04074926059809401</v>
       </c>
       <c r="AK2">
-        <v>0.1202903560318009</v>
+        <v>0.04133333333333335</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -703,6 +709,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.105</v>
+      </c>
+      <c r="E3">
+        <v>0.09</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -716,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>37.2</v>
+        <v>42.7</v>
       </c>
       <c r="L3">
-        <v>0.2717311906501096</v>
+        <v>0.2896879240162822</v>
       </c>
       <c r="M3">
-        <v>0.001</v>
+        <v>7.8</v>
       </c>
       <c r="N3">
-        <v>3.743916136278547e-06</v>
+        <v>0.02672147995889003</v>
       </c>
       <c r="O3">
-        <v>2.688172043010753e-05</v>
+        <v>0.1826697892271663</v>
       </c>
       <c r="P3">
-        <v>0.001</v>
+        <v>7.8</v>
       </c>
       <c r="Q3">
-        <v>3.743916136278547e-06</v>
+        <v>0.02672147995889003</v>
       </c>
       <c r="R3">
-        <v>2.688172043010753e-05</v>
+        <v>0.1826697892271663</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -746,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>46.3</v>
+        <v>59.3</v>
       </c>
       <c r="V3">
-        <v>0.1733433171096967</v>
+        <v>0.2031517643028435</v>
       </c>
       <c r="W3">
-        <v>0.1482662415304903</v>
+        <v>0.157390342793955</v>
       </c>
       <c r="X3">
-        <v>0.143962184879353</v>
+        <v>0.1233396199045744</v>
       </c>
       <c r="Y3">
-        <v>0.004304056651137284</v>
+        <v>0.03405072288938064</v>
       </c>
       <c r="Z3">
-        <v>0.4321447511300791</v>
+        <v>0.4484427718265981</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.140236647295106</v>
+        <v>0.1230077050576663</v>
       </c>
       <c r="AC3">
-        <v>-0.140236647295106</v>
+        <v>-0.1230077050576663</v>
       </c>
       <c r="AD3">
-        <v>81.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>81.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="AG3">
-        <v>34.8</v>
+        <v>12.40000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.232912119471568</v>
+        <v>0.1971947194719472</v>
       </c>
       <c r="AI3">
-        <v>0.2416567342073897</v>
+        <v>0.1995546896743668</v>
       </c>
       <c r="AJ3">
-        <v>0.1152699569393839</v>
+        <v>0.04074926059809401</v>
       </c>
       <c r="AK3">
-        <v>0.1202903560318009</v>
+        <v>0.04133333333333335</v>
       </c>
       <c r="AL3">
         <v>0</v>
